--- a/survey_templates/049_roundabout_issues_survey--survey_templates.xlsx
+++ b/survey_templates/049_roundabout_issues_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'roundabout'}</t>
+          <t>roundabout</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'roundabout'}</t>
+          <t>roundabout</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'traffic_circle'}</t>
+          <t>traffic_circle</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'traffic_circle'}</t>
+          <t>traffic circle</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'turn_lane'}</t>
+          <t>turn_lane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'turn_lane'}</t>
+          <t>turn lane</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'too_fast'}</t>
+          <t>too_fast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'too_fast'}</t>
+          <t>too fast</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'too_slow'}</t>
+          <t>too_slow</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'too_slow'}</t>
+          <t>too slow</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_enough_signage'}</t>
+          <t>not_enough_signage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_enough_signage'}</t>
+          <t>not enough signage</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'too_narrow'}</t>
+          <t>too_narrow</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'too_narrow'}</t>
+          <t>too narrow</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'not_enough_space'}</t>
+          <t>not_enough_space</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'not_enough_space'}</t>
+          <t>not enough space</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
